--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/phi-4/metrics_default_vs_aae.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/phi-4/metrics_default_vs_aae.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.946236559139785</v>
+        <v>0.9157894736842105</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.7183098591549296</v>
+        <v>0.6971830985915493</v>
       </c>
       <c r="D2">
-        <v>0.3125</v>
+        <v>0.3307692307692308</v>
       </c>
       <c r="E2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F2">
         <v>35</v>
       </c>
       <c r="G2">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
